--- a/data/samples/classes.xlsx
+++ b/data/samples/classes.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1da8a374996541b6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R413dd2d9adf04fc3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -152,12 +152,58 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="dk1"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="accent1"/>
-        </a:solidFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="67000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="73000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="81000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="94000"/>
+                <a:lumMod val="102000"/>
+                <a:satMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:shade val="100000"/>
+                <a:lumMod val="100000"/>
+                <a:satMod val="110000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="78000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="12700">
@@ -431,7 +477,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7b18ec054595451b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1738a0d0c16d4c1f"/>
   </x:tableParts>
 </x:worksheet>
 </file>